--- a/backend/data-filtering/schedule_table_2.xlsx
+++ b/backend/data-filtering/schedule_table_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\travel\backend\data-filtering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD9E571-FB13-417A-9879-78C90014DF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C12E6A5-2A0D-49E6-8D61-C975F632A38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="719">
   <si>
     <t>schedule_id</t>
   </si>
@@ -37,8 +37,7 @@
     <t>days_of_week</t>
   </si>
   <si>
-    <t>WRSCH_98702
-GN 2</t>
+    <t>HRSPV_98702</t>
   </si>
   <si>
     <t>HRTR0156OR</t>
@@ -50,8 +49,7 @@
     <t>00:07</t>
   </si>
   <si>
-    <t>WRSCH_98002
-PL 2</t>
+    <t>HRSPV_98002</t>
   </si>
   <si>
     <t>HRTR0157FT</t>
@@ -63,8 +61,7 @@
     <t>00:03</t>
   </si>
   <si>
-    <t>WRSCH_98802
-B 2</t>
+    <t>HRSPV_98802</t>
   </si>
   <si>
     <t>HRTR0158OR</t>
@@ -76,9 +73,7 @@
     <t>04:17</t>
   </si>
   <si>
-    <t>WRSCH_98502
-V 2
-X</t>
+    <t>HRSPV_98502</t>
   </si>
   <si>
     <t>HRTR0159FT</t>
@@ -90,8 +85,7 @@
     <t>04:03</t>
   </si>
   <si>
-    <t>WRSCH_98302
-BR 2</t>
+    <t>HRSPV_98302</t>
   </si>
   <si>
     <t>HRTR0160FT</t>
@@ -103,16 +97,13 @@
     <t>03:55</t>
   </si>
   <si>
-    <t>WRSCH_98804
-B 4</t>
+    <t>HRSPV_98804</t>
   </si>
   <si>
     <t>04:34</t>
   </si>
   <si>
-    <t>WRSCH_98506
-VVD 2
-X</t>
+    <t>HRSPV_98506</t>
   </si>
   <si>
     <t>HRTR0161FT</t>
@@ -121,69 +112,58 @@
     <t>04:15</t>
   </si>
   <si>
-    <t>WRSCH_98504
-V 4</t>
+    <t>HRSPV_98504</t>
   </si>
   <si>
     <t>04:25</t>
   </si>
   <si>
-    <t>WRSCH_98304
-BR 4</t>
+    <t>HRSPV_98304</t>
   </si>
   <si>
     <t>04:13</t>
   </si>
   <si>
-    <t>WRSCH_98004
-PL 4</t>
-  </si>
-  <si>
-    <t>WRSCH_98508
-V 6</t>
+    <t>HRSPV_98004</t>
+  </si>
+  <si>
+    <t>HRSPV_98508</t>
   </si>
   <si>
     <t>04:37</t>
   </si>
   <si>
-    <t>WRSCH_98306
-BR 6</t>
+    <t>HRSPV_98306</t>
   </si>
   <si>
     <t>04:26</t>
   </si>
   <si>
-    <t>WRSCH_98510
-V 8</t>
+    <t>HRSPV_98510</t>
   </si>
   <si>
     <t>04:50</t>
   </si>
   <si>
-    <t>WRSCH_98806
-B 6</t>
+    <t>HRSPV_98806</t>
   </si>
   <si>
     <t>05:13</t>
   </si>
   <si>
-    <t>WRSCH_98006
-PL 6</t>
+    <t>HRSPV_98006</t>
   </si>
   <si>
     <t>04:27</t>
   </si>
   <si>
-    <t>WRSCH_98512
-VVD 4
-X</t>
+    <t>HRSPV_98512</t>
   </si>
   <si>
     <t>05:04</t>
   </si>
   <si>
-    <t>WRSCH_99002
-TPL 2</t>
+    <t>HRSPV_99002</t>
   </si>
   <si>
     <t>HRTR0162OR</t>
@@ -192,114 +172,94 @@
     <t>04:33</t>
   </si>
   <si>
-    <t>WRSCH_98308
-BR 8</t>
+    <t>HRSPV_98308</t>
   </si>
   <si>
     <t>04:53</t>
   </si>
   <si>
-    <t>WRSCH_98704
-GN 4</t>
+    <t>HRSPV_98704</t>
   </si>
   <si>
     <t>05:05</t>
   </si>
   <si>
-    <t>WRSCH_98514
-V 10
-X</t>
+    <t>HRSPV_98514</t>
   </si>
   <si>
     <t>05:15</t>
   </si>
   <si>
-    <t>WRSCH_98008
-PL 8</t>
+    <t>HRSPV_98008</t>
   </si>
   <si>
     <t>04:49</t>
   </si>
   <si>
-    <t>WRSCH_98706
-GN 6</t>
+    <t>HRSPV_98706</t>
   </si>
   <si>
     <t>05:17</t>
   </si>
   <si>
-    <t>WRSCH_99004
-TPL 4</t>
-  </si>
-  <si>
-    <t>WRSCH_98516
-V 12</t>
+    <t>HRSPV_99004</t>
+  </si>
+  <si>
+    <t>HRSPV_98516</t>
   </si>
   <si>
     <t>05:27</t>
   </si>
   <si>
-    <t>WRSCH_98010
-PL 10</t>
-  </si>
-  <si>
-    <t>WRSCH_98708
-GN 8</t>
+    <t>HRSPV_98010</t>
+  </si>
+  <si>
+    <t>HRSPV_98708</t>
   </si>
   <si>
     <t>05:33</t>
   </si>
   <si>
-    <t>WRSCH_98518
-V 14</t>
+    <t>HRSPV_98518</t>
   </si>
   <si>
     <t>05:43</t>
   </si>
   <si>
-    <t>WRSCH_98012
-PL 12</t>
-  </si>
-  <si>
-    <t>WRSCH_99006
-TPL 6</t>
+    <t>HRSPV_98012</t>
+  </si>
+  <si>
+    <t>HRSPV_99006</t>
   </si>
   <si>
     <t>05:21</t>
   </si>
   <si>
-    <t>WRSCH_98808
-B 8</t>
+    <t>HRSPV_98808</t>
   </si>
   <si>
     <t>06:10</t>
   </si>
   <si>
-    <t>WRSCH_98310
-BR 10</t>
+    <t>HRSPV_98310</t>
   </si>
   <si>
     <t>05:40</t>
   </si>
   <si>
-    <t>WRSCH_98014
-PL 14</t>
+    <t>HRSPV_98014</t>
   </si>
   <si>
     <t>05:31</t>
   </si>
   <si>
-    <t>WRSCH_98710
-GN 10
-X</t>
+    <t>HRSPV_98710</t>
   </si>
   <si>
     <t>05:59</t>
   </si>
   <si>
-    <t>WRSCH_98312
-BRVD 2
-X</t>
+    <t>HRSPV_98312</t>
   </si>
   <si>
     <t>HRTR0163FT</t>
@@ -308,48 +268,40 @@
     <t>05:50</t>
   </si>
   <si>
-    <t>WRSCH_98016
-PL 16</t>
-  </si>
-  <si>
-    <t>WRSCH_99008
-TPL 8
-X</t>
+    <t>HRSPV_98016</t>
+  </si>
+  <si>
+    <t>HRSPV_99008</t>
   </si>
   <si>
     <t>05:44</t>
   </si>
   <si>
-    <t>WRSCH_98520
-V 16</t>
+    <t>HRSPV_98520</t>
   </si>
   <si>
     <t>06:16</t>
   </si>
   <si>
-    <t>WRSCH_98712
-GN 12</t>
+    <t>HRSPV_98712</t>
   </si>
   <si>
     <t>06:14</t>
   </si>
   <si>
-    <t>WRSCH_98314
-BR 12</t>
+    <t>HRSPV_98314</t>
   </si>
   <si>
     <t>06:08</t>
   </si>
   <si>
-    <t>WRSCH_98810
-B 10</t>
+    <t>HRSPV_98810</t>
   </si>
   <si>
     <t>06:45</t>
   </si>
   <si>
-    <t>WRSCH_98901
-PLGN 1</t>
+    <t>HRSPV_98901</t>
   </si>
   <si>
     <t>HRTR0164FT</t>
@@ -358,145 +310,121 @@
     <t>05:57</t>
   </si>
   <si>
-    <t>WRSCH_98018
-PL 18</t>
+    <t>HRSPV_98018</t>
   </si>
   <si>
     <t>06:02</t>
   </si>
   <si>
-    <t>WRSCH_98316
-BR 14</t>
+    <t>HRSPV_98316</t>
   </si>
   <si>
     <t>06:22</t>
   </si>
   <si>
-    <t>WRSCH_98714
-GN 14</t>
+    <t>HRSPV_98714</t>
   </si>
   <si>
     <t>06:35</t>
   </si>
   <si>
-    <t>WRSCH_99010
-TPL 10</t>
+    <t>HRSPV_99010</t>
   </si>
   <si>
     <t>06:13</t>
   </si>
   <si>
-    <t>WRSCH_98020
-PL 20
-X</t>
+    <t>HRSPV_98020</t>
   </si>
   <si>
     <t>06:17</t>
   </si>
   <si>
-    <t>WRSCH_98812
-B 12</t>
+    <t>HRSPV_98812</t>
   </si>
   <si>
     <t>07:13</t>
   </si>
   <si>
-    <t>WRSCH_98522
-VVD 6
-X</t>
+    <t>HRSPV_98522</t>
   </si>
   <si>
     <t>06:55</t>
   </si>
   <si>
-    <t>WRSCH_98022
-PL 22</t>
+    <t>HRSPV_98022</t>
   </si>
   <si>
     <t>06:29</t>
   </si>
   <si>
-    <t>WRSCH_98716
-GN 16</t>
+    <t>HRSPV_98716</t>
   </si>
   <si>
     <t>06:57</t>
   </si>
   <si>
-    <t>WRSCH_98524
-V 18</t>
+    <t>HRSPV_98524</t>
   </si>
   <si>
     <t>07:07</t>
   </si>
   <si>
-    <t>WRSCH_99012
-TPL 12</t>
+    <t>HRSPV_99012</t>
   </si>
   <si>
     <t>06:37</t>
   </si>
   <si>
-    <t>WRSCH_98814
-B 14</t>
+    <t>HRSPV_98814</t>
   </si>
   <si>
     <t>07:29</t>
   </si>
   <si>
-    <t>WRSCH_98024
-PLVD 2</t>
+    <t>HRSPV_98024</t>
   </si>
   <si>
     <t>06:41</t>
   </si>
   <si>
-    <t>WRSCH_98026
-PL 24</t>
-  </si>
-  <si>
-    <t>WRSCH_98318
-BR 16
-X</t>
+    <t>HRSPV_98026</t>
+  </si>
+  <si>
+    <t>HRSPV_98318</t>
   </si>
   <si>
     <t>07:04</t>
   </si>
   <si>
-    <t>WRSCH_98718
-GN 18</t>
+    <t>HRSPV_98718</t>
   </si>
   <si>
     <t>07:17</t>
   </si>
   <si>
-    <t>WRSCH_98903
-PLGN 3</t>
+    <t>HRSPV_98903</t>
   </si>
   <si>
     <t>06:53</t>
   </si>
   <si>
-    <t>WRSCH_98028
-PL 26</t>
-  </si>
-  <si>
-    <t>WRSCH_99014
-TPL 14</t>
+    <t>HRSPV_98028</t>
+  </si>
+  <si>
+    <t>HRSPV_99014</t>
   </si>
   <si>
     <t>07:01</t>
   </si>
   <si>
-    <t>WRSCH_98526
-V 20</t>
+    <t>HRSPV_98526</t>
   </si>
   <si>
     <t>07:31</t>
   </si>
   <si>
-    <t>WRSCH_98902
-GNPL 2</t>
+    <t>HRSPV_98902</t>
   </si>
   <si>
     <t>HRTR0165OR</t>
@@ -505,66 +433,55 @@
     <t>07:30</t>
   </si>
   <si>
-    <t>WRSCH_98320
-BR 18</t>
+    <t>HRSPV_98320</t>
   </si>
   <si>
     <t>07:20</t>
   </si>
   <si>
-    <t>WRSCH_98030
-PLVD 4
-X</t>
+    <t>HRSPV_98030</t>
   </si>
   <si>
     <t>07:09</t>
   </si>
   <si>
-    <t>WRSCH_98816
-B 16</t>
+    <t>HRSPV_98816</t>
   </si>
   <si>
     <t>07:58</t>
   </si>
   <si>
-    <t>WRSCH_98032
-PL 28</t>
+    <t>HRSPV_98032</t>
   </si>
   <si>
     <t>07:14</t>
   </si>
   <si>
-    <t>WRSCH_98528
-V 22</t>
+    <t>HRSPV_98528</t>
   </si>
   <si>
     <t>07:48</t>
   </si>
   <si>
-    <t>WRSCH_99016
-TPL 16</t>
+    <t>HRSPV_99016</t>
   </si>
   <si>
     <t>07:18</t>
   </si>
   <si>
-    <t>WRSCH_98034
-PLVD 6
-X</t>
+    <t>HRSPV_98034</t>
   </si>
   <si>
     <t>07:22</t>
   </si>
   <si>
-    <t>WRSCH_98720
-GN 20</t>
+    <t>HRSPV_98720</t>
   </si>
   <si>
     <t>07:47</t>
   </si>
   <si>
-    <t>WRSCH_98602
-M 2</t>
+    <t>HRSPV_98602</t>
   </si>
   <si>
     <t>HRTR0166FT</t>
@@ -576,155 +493,130 @@
     <t>08:05</t>
   </si>
   <si>
-    <t>WRSCH_98036
-PL 30</t>
-  </si>
-  <si>
-    <t>WRSCH_98322
-BR 20</t>
+    <t>HRSPV_98036</t>
+  </si>
+  <si>
+    <t>HRSPV_98322</t>
   </si>
   <si>
     <t>07:50</t>
   </si>
   <si>
-    <t>WRSCH_98905
-PLGN 5</t>
+    <t>HRSPV_98905</t>
   </si>
   <si>
     <t>07:39</t>
   </si>
   <si>
-    <t>WRSCH_98818
-B 18</t>
+    <t>HRSPV_98818</t>
   </si>
   <si>
     <t>08:28</t>
   </si>
   <si>
-    <t>WRSCH_99018
-TPL 18</t>
+    <t>HRSPV_99018</t>
   </si>
   <si>
     <t>07:43</t>
   </si>
   <si>
-    <t>WRSCH_98530
-V 24</t>
+    <t>HRSPV_98530</t>
   </si>
   <si>
     <t>08:13</t>
   </si>
   <si>
-    <t>WRSCH_98038
-PL 32</t>
-  </si>
-  <si>
-    <t>WRSCH_98324
-BR 22</t>
+    <t>HRSPV_98038</t>
+  </si>
+  <si>
+    <t>HRSPV_98324</t>
   </si>
   <si>
     <t>08:06</t>
   </si>
   <si>
-    <t>WRSCH_98722
-GN 22</t>
+    <t>HRSPV_98722</t>
   </si>
   <si>
     <t>08:17</t>
   </si>
   <si>
-    <t>WRSCH_98040
-PLVD 8</t>
+    <t>HRSPV_98040</t>
   </si>
   <si>
     <t>07:55</t>
   </si>
   <si>
-    <t>WRSCH_98042
-PL 34
-$ X</t>
+    <t>HRSPV_98042</t>
   </si>
   <si>
     <t>07:59</t>
   </si>
   <si>
-    <t>WRSCH_99020
-TPL 20</t>
+    <t>HRSPV_99020</t>
   </si>
   <si>
     <t>08:04</t>
   </si>
   <si>
-    <t>WRSCH_98532
-V 26</t>
+    <t>HRSPV_98532</t>
   </si>
   <si>
     <t>08:33</t>
   </si>
   <si>
-    <t>WRSCH_98820
-B 20</t>
+    <t>HRSPV_98820</t>
   </si>
   <si>
     <t>08:53</t>
   </si>
   <si>
-    <t>WRSCH_98044
-PL 36</t>
+    <t>HRSPV_98044</t>
   </si>
   <si>
     <t>08:09</t>
   </si>
   <si>
-    <t>WRSCH_98604
-M 4
-X</t>
-  </si>
-  <si>
-    <t>WRSCH_99022
-TPL 22</t>
+    <t>HRSPV_98604</t>
+  </si>
+  <si>
+    <t>HRSPV_99022</t>
   </si>
   <si>
     <t>08:15</t>
   </si>
   <si>
-    <t>WRSCH_98904
-GNPL 4</t>
+    <t>HRSPV_98904</t>
   </si>
   <si>
     <t>08:39</t>
   </si>
   <si>
-    <t>WRSCH_98046
-PL 38 L/SPL X</t>
+    <t>HRSPV_98046</t>
   </si>
   <si>
     <t>08:19</t>
   </si>
   <si>
-    <t>WRSCH_98822
-B 22</t>
+    <t>HRSPV_98822</t>
   </si>
   <si>
     <t>09:08</t>
   </si>
   <si>
-    <t>WRSCH_98048
-PL 40</t>
+    <t>HRSPV_98048</t>
   </si>
   <si>
     <t>08:26</t>
   </si>
   <si>
-    <t>WRSCH_98724
-GN 24</t>
+    <t>HRSPV_98724</t>
   </si>
   <si>
     <t>08:51</t>
   </si>
   <si>
-    <t>WRSCH_98606
-CM 2</t>
+    <t>HRSPV_98606</t>
   </si>
   <si>
     <t>HRTR0167FT</t>
@@ -736,1760 +628,1459 @@
     <t>09:14</t>
   </si>
   <si>
-    <t>WRSCH_98326
-BR 24
-X</t>
+    <t>HRSPV_98326</t>
   </si>
   <si>
     <t>08:49</t>
   </si>
   <si>
-    <t>WRSCH_98050
-PLVD 10</t>
+    <t>HRSPV_98050</t>
   </si>
   <si>
     <t>08:38</t>
   </si>
   <si>
-    <t>WRSCH_98824
-B 24</t>
+    <t>HRSPV_98824</t>
   </si>
   <si>
     <t>09:27</t>
   </si>
   <si>
-    <t>WRSCH_98534
-V 28
-$</t>
+    <t>HRSPV_98534</t>
   </si>
   <si>
     <t>09:12</t>
   </si>
   <si>
-    <t>WRSCH_98052
-PL 42</t>
+    <t>HRSPV_98052</t>
   </si>
   <si>
     <t>08:45</t>
   </si>
   <si>
-    <t>WRSCH_98726
-GN 26</t>
+    <t>HRSPV_98726</t>
   </si>
   <si>
     <t>09:13</t>
   </si>
   <si>
-    <t>WRSCH_98054
-PLVD 12
-X</t>
-  </si>
-  <si>
-    <t>WRSCH_98328
-BR 26</t>
+    <t>HRSPV_98054</t>
+  </si>
+  <si>
+    <t>HRSPV_98328</t>
   </si>
   <si>
     <t>09:07</t>
   </si>
   <si>
-    <t>WRSCH_98056
-PL 44</t>
+    <t>HRSPV_98056</t>
   </si>
   <si>
     <t>08:56</t>
   </si>
   <si>
-    <t>WRSCH_99024
-TPL 24
-$</t>
+    <t>HRSPV_99024</t>
   </si>
   <si>
     <t>09:01</t>
   </si>
   <si>
-    <t>WRSCH_98826
-B 26</t>
+    <t>HRSPV_98826</t>
   </si>
   <si>
     <t>09:51</t>
   </si>
   <si>
-    <t>WRSCH_98330
-BR 28
-X</t>
+    <t>HRSPV_98330</t>
   </si>
   <si>
     <t>09:20</t>
   </si>
   <si>
-    <t>WRSCH_98906
-GNPL 6</t>
+    <t>HRSPV_98906</t>
   </si>
   <si>
     <t>09:30</t>
   </si>
   <si>
-    <t>WRSCH_98058
-PL 46</t>
+    <t>HRSPV_98058</t>
   </si>
   <si>
     <t>09:09</t>
   </si>
   <si>
-    <t>WRSCH_98536
-V 30</t>
+    <t>HRSPV_98536</t>
   </si>
   <si>
     <t>09:44</t>
   </si>
   <si>
-    <t>WRSCH_98060
-PL 48</t>
+    <t>HRSPV_98060</t>
   </si>
   <si>
     <t>09:17</t>
   </si>
   <si>
-    <t>WRSCH_98728
-GN 28</t>
+    <t>HRSPV_98728</t>
   </si>
   <si>
     <t>09:46</t>
   </si>
   <si>
-    <t>WRSCH_98332
-BR 30</t>
+    <t>HRSPV_98332</t>
   </si>
   <si>
     <t>09:39</t>
   </si>
   <si>
-    <t>WRSCH_98062
-PL 50</t>
+    <t>HRSPV_98062</t>
   </si>
   <si>
     <t>09:28</t>
   </si>
   <si>
-    <t>WRSCH_98064
-PLVD 14
-X</t>
+    <t>HRSPV_98064</t>
   </si>
   <si>
     <t>09:32</t>
   </si>
   <si>
-    <t>WRSCH_98828
-B 28</t>
+    <t>HRSPV_98828</t>
   </si>
   <si>
     <t>10:20</t>
   </si>
   <si>
-    <t>WRSCH_98538
-V 32</t>
+    <t>HRSPV_98538</t>
   </si>
   <si>
     <t>10:07</t>
   </si>
   <si>
-    <t>WRSCH_98066
-PL 52</t>
+    <t>HRSPV_98066</t>
   </si>
   <si>
     <t>09:40</t>
   </si>
   <si>
-    <t>WRSCH_98730
-GN 30</t>
+    <t>HRSPV_98730</t>
   </si>
   <si>
     <t>10:06</t>
   </si>
   <si>
-    <t>WRSCH_98068
-PLVD 16
-X</t>
-  </si>
-  <si>
-    <t>WRSCH_98540
-V 34
-X</t>
+    <t>HRSPV_98068</t>
+  </si>
+  <si>
+    <t>HRSPV_98540</t>
   </si>
   <si>
     <t>10:19</t>
   </si>
   <si>
-    <t>WRSCH_99026
-TPL 26</t>
+    <t>HRSPV_99026</t>
   </si>
   <si>
     <t>09:48</t>
   </si>
   <si>
-    <t>WRSCH_98070
-PL 54</t>
+    <t>HRSPV_98070</t>
   </si>
   <si>
     <t>09:53</t>
   </si>
   <si>
-    <t>WRSCH_98830
-B 30</t>
+    <t>HRSPV_98830</t>
   </si>
   <si>
     <t>10:45</t>
   </si>
   <si>
-    <t>WRSCH_98334
-BR 32</t>
+    <t>HRSPV_98334</t>
   </si>
   <si>
     <t>10:16</t>
   </si>
   <si>
-    <t>WRSCH_98072
-PL 56</t>
+    <t>HRSPV_98072</t>
   </si>
   <si>
     <t>10:05</t>
   </si>
   <si>
-    <t>WRSCH_99028
-TPL 28</t>
+    <t>HRSPV_99028</t>
   </si>
   <si>
     <t>10:12</t>
   </si>
   <si>
-    <t>WRSCH_98732
-GN 32</t>
+    <t>HRSPV_98732</t>
   </si>
   <si>
     <t>10:35</t>
   </si>
   <si>
-    <t>WRSCH_98074
-PL 58</t>
+    <t>HRSPV_98074</t>
   </si>
   <si>
     <t>10:17</t>
   </si>
   <si>
-    <t>WRSCH_98076
-PLVD 18</t>
+    <t>HRSPV_98076</t>
   </si>
   <si>
     <t>10:21</t>
   </si>
   <si>
-    <t>WRSCH_98336
-BR 34</t>
+    <t>HRSPV_98336</t>
   </si>
   <si>
     <t>10:40</t>
   </si>
   <si>
-    <t>WRSCH_98832
-B 32</t>
+    <t>HRSPV_98832</t>
   </si>
   <si>
     <t>11:17</t>
   </si>
   <si>
-    <t>WRSCH_98078
-PL 60</t>
+    <t>HRSPV_98078</t>
   </si>
   <si>
     <t>10:33</t>
   </si>
   <si>
-    <t>WRSCH_98907
-PLGN 7</t>
+    <t>HRSPV_98907</t>
   </si>
   <si>
     <t>10:37</t>
   </si>
   <si>
-    <t>WRSCH_99030
-TPL 30</t>
+    <t>HRSPV_99030</t>
   </si>
   <si>
     <t>10:41</t>
   </si>
   <si>
-    <t>WRSCH_98734
-GN 34</t>
+    <t>HRSPV_98734</t>
   </si>
   <si>
     <t>11:00</t>
   </si>
   <si>
-    <t>WRSCH_98338
-BR 36
-X</t>
+    <t>HRSPV_98338</t>
   </si>
   <si>
     <t>10:59</t>
   </si>
   <si>
-    <t>WRSCH_98080
-PL 62</t>
+    <t>HRSPV_98080</t>
   </si>
   <si>
     <t>10:49</t>
   </si>
   <si>
-    <t>WRSCH_98834
-B 34</t>
+    <t>HRSPV_98834</t>
   </si>
   <si>
     <t>11:41</t>
   </si>
   <si>
-    <t>WRSCH_98340
-BR 38
-X</t>
+    <t>HRSPV_98340</t>
   </si>
   <si>
     <t>11:13</t>
   </si>
   <si>
-    <t>WRSCH_99032
-TPL 32</t>
+    <t>HRSPV_99032</t>
   </si>
   <si>
     <t>11:02</t>
   </si>
   <si>
-    <t>WRSCH_98736
-GN 36</t>
+    <t>HRSPV_98736</t>
   </si>
   <si>
     <t>11:23</t>
   </si>
   <si>
-    <t>WRSCH_98082
-PL 64</t>
+    <t>HRSPV_98082</t>
   </si>
   <si>
     <t>11:06</t>
   </si>
   <si>
-    <t>WRSCH_91392
-WGN 2
-X</t>
+    <t>HRSPV_91392</t>
   </si>
   <si>
     <t>11:34</t>
   </si>
   <si>
-    <t>WRSCH_98084
-PLVD 20
-X</t>
+    <t>HRSPV_98084</t>
   </si>
   <si>
     <t>11:10</t>
   </si>
   <si>
-    <t>WRSCH_98086
-PL 66</t>
+    <t>HRSPV_98086</t>
   </si>
   <si>
     <t>11:16</t>
   </si>
   <si>
-    <t>WRSCH_98342
-BR 40</t>
+    <t>HRSPV_98342</t>
   </si>
   <si>
     <t>11:39</t>
   </si>
   <si>
-    <t>WRSCH_98088
-PLVD 22</t>
+    <t>HRSPV_98088</t>
   </si>
   <si>
     <t>11:28</t>
   </si>
   <si>
-    <t>WRSCH_98836
-B 36</t>
+    <t>HRSPV_98836</t>
   </si>
   <si>
     <t>12:16</t>
   </si>
   <si>
-    <t>WRSCH_98090
-PL 68</t>
+    <t>HRSPV_98090</t>
   </si>
   <si>
     <t>11:32</t>
   </si>
   <si>
-    <t>WRSCH_98738
-GN 38</t>
+    <t>HRSPV_98738</t>
   </si>
   <si>
     <t>11:54</t>
   </si>
   <si>
-    <t>WRSCH_98344
-BR 42
-X</t>
-  </si>
-  <si>
-    <t>WRSCH_98092
-PL 70</t>
+    <t>HRSPV_98344</t>
+  </si>
+  <si>
+    <t>HRSPV_98092</t>
   </si>
   <si>
     <t>11:43</t>
   </si>
   <si>
-    <t>WRSCH_98838
-B 38</t>
+    <t>HRSPV_98838</t>
   </si>
   <si>
     <t>12:37</t>
   </si>
   <si>
-    <t>WRSCH_98094
-PL 72</t>
+    <t>HRSPV_98094</t>
   </si>
   <si>
     <t>11:52</t>
   </si>
   <si>
-    <t>WRSCH_98908
-GNPL 8</t>
+    <t>HRSPV_98908</t>
   </si>
   <si>
     <t>12:14</t>
   </si>
   <si>
-    <t>WRSCH_98346
-BR 44</t>
+    <t>HRSPV_98346</t>
   </si>
   <si>
     <t>12:11</t>
   </si>
   <si>
-    <t>WRSCH_98740
-GN 40</t>
+    <t>HRSPV_98740</t>
   </si>
   <si>
     <t>12:27</t>
   </si>
   <si>
-    <t>WRSCH_98096
-PLVD 24</t>
+    <t>HRSPV_98096</t>
   </si>
   <si>
     <t>12:03</t>
   </si>
   <si>
-    <t>WRSCH_98098
-PL 74</t>
+    <t>HRSPV_98098</t>
   </si>
   <si>
     <t>12:07</t>
   </si>
   <si>
-    <t>WRSCH_98840
-B 40</t>
+    <t>HRSPV_98840</t>
   </si>
   <si>
     <t>12:58</t>
   </si>
   <si>
-    <t>WRSCH_98348
-BR 46</t>
+    <t>HRSPV_98348</t>
   </si>
   <si>
     <t>12:29</t>
   </si>
   <si>
-    <t>WRSCH_99034
-TPL 34</t>
+    <t>HRSPV_99034</t>
   </si>
   <si>
     <t>12:19</t>
   </si>
   <si>
-    <t>WRSCH_98100
-PL 76</t>
+    <t>HRSPV_98100</t>
   </si>
   <si>
     <t>12:24</t>
   </si>
   <si>
-    <t>WRSCH_98742
-GN 42</t>
+    <t>HRSPV_98742</t>
   </si>
   <si>
     <t>12:53</t>
   </si>
   <si>
-    <t>WRSCH_98350
-BR 48</t>
+    <t>HRSPV_98350</t>
   </si>
   <si>
     <t>12:48</t>
   </si>
   <si>
-    <t>WRSCH_98842
-B 42</t>
+    <t>HRSPV_98842</t>
   </si>
   <si>
     <t>13:24</t>
   </si>
   <si>
-    <t>WRSCH_98102
-PL 78</t>
+    <t>HRSPV_98102</t>
   </si>
   <si>
     <t>12:41</t>
   </si>
   <si>
-    <t>WRSCH_98104
-PLVD 26</t>
+    <t>HRSPV_98104</t>
   </si>
   <si>
     <t>12:49</t>
   </si>
   <si>
-    <t>WRSCH_98744
-GN 44</t>
+    <t>HRSPV_98744</t>
   </si>
   <si>
     <t>13:15</t>
   </si>
   <si>
-    <t>WRSCH_98106
-PL 80</t>
+    <t>HRSPV_98106</t>
   </si>
   <si>
     <t>12:56</t>
   </si>
   <si>
-    <t>WRSCH_98844
-B 44</t>
+    <t>HRSPV_98844</t>
   </si>
   <si>
     <t>13:51</t>
   </si>
   <si>
-    <t>WRSCH_99036
-TPL 36</t>
+    <t>HRSPV_99036</t>
   </si>
   <si>
     <t>13:04</t>
   </si>
   <si>
-    <t>WRSCH_98108
-PL 82</t>
+    <t>HRSPV_98108</t>
   </si>
   <si>
     <t>13:09</t>
   </si>
   <si>
-    <t>WRSCH_91394
-WGN 4
-X</t>
+    <t>HRSPV_91394</t>
   </si>
   <si>
     <t>13:38</t>
   </si>
   <si>
-    <t>WRSCH_98110
-PL 84</t>
+    <t>HRSPV_98110</t>
   </si>
   <si>
     <t>13:19</t>
   </si>
   <si>
-    <t>WRSCH_98112
-PL 86
-X</t>
+    <t>HRSPV_98112</t>
   </si>
   <si>
     <t>13:23</t>
   </si>
   <si>
-    <t>WRSCH_98352
-BRVD 4</t>
+    <t>HRSPV_98352</t>
   </si>
   <si>
     <t>13:41</t>
   </si>
   <si>
-    <t>WRSCH_98846
-B 46</t>
+    <t>HRSPV_98846</t>
   </si>
   <si>
     <t>14:17</t>
   </si>
   <si>
-    <t>WRSCH_98114
-PL 88
-X</t>
+    <t>HRSPV_98114</t>
   </si>
   <si>
     <t>13:33</t>
   </si>
   <si>
-    <t>WRSCH_98116
-PL 90</t>
+    <t>HRSPV_98116</t>
   </si>
   <si>
     <t>13:37</t>
   </si>
   <si>
-    <t>WRSCH_98746
-GN 46</t>
+    <t>HRSPV_98746</t>
   </si>
   <si>
     <t>14:05</t>
   </si>
   <si>
-    <t>WRSCH_98118
-PL 92
-X</t>
+    <t>HRSPV_98118</t>
   </si>
   <si>
     <t>13:45</t>
   </si>
   <si>
-    <t>WRSCH_98354
-BR 50</t>
+    <t>HRSPV_98354</t>
   </si>
   <si>
     <t>14:04</t>
   </si>
   <si>
-    <t>WRSCH_98848
-B 48</t>
+    <t>HRSPV_98848</t>
   </si>
   <si>
     <t>14:41</t>
   </si>
   <si>
-    <t>WRSCH_98120
-PL 94</t>
+    <t>HRSPV_98120</t>
   </si>
   <si>
     <t>13:57</t>
   </si>
   <si>
-    <t>WRSCH_99038
-TPL 38</t>
+    <t>HRSPV_99038</t>
   </si>
   <si>
     <t>14:01</t>
   </si>
   <si>
-    <t>WRSCH_98542
-V 36</t>
+    <t>HRSPV_98542</t>
   </si>
   <si>
     <t>14:31</t>
   </si>
   <si>
-    <t>WRSCH_98122
-PL 96</t>
-  </si>
-  <si>
-    <t>WRSCH_98124
-PLVD 28</t>
+    <t>HRSPV_98122</t>
+  </si>
+  <si>
+    <t>HRSPV_98124</t>
   </si>
   <si>
     <t>14:09</t>
   </si>
   <si>
-    <t>WRSCH_98748
-GN 48</t>
+    <t>HRSPV_98748</t>
   </si>
   <si>
     <t>14:33</t>
   </si>
   <si>
-    <t>WRSCH_98356
-BR 52</t>
+    <t>HRSPV_98356</t>
   </si>
   <si>
     <t>14:28</t>
   </si>
   <si>
-    <t>WRSCH_98850
-B 50</t>
+    <t>HRSPV_98850</t>
   </si>
   <si>
     <t>15:05</t>
   </si>
   <si>
-    <t>WRSCH_98126
-PL 98</t>
+    <t>HRSPV_98126</t>
   </si>
   <si>
     <t>14:20</t>
   </si>
   <si>
-    <t>WRSCH_99040
-TPL 40</t>
+    <t>HRSPV_99040</t>
   </si>
   <si>
     <t>14:24</t>
   </si>
   <si>
-    <t>WRSCH_98128
-PL 100</t>
-  </si>
-  <si>
-    <t>WRSCH_98750
-GN 50</t>
+    <t>HRSPV_98128</t>
+  </si>
+  <si>
+    <t>HRSPV_98750</t>
   </si>
   <si>
     <t>14:59</t>
   </si>
   <si>
-    <t>WRSCH_98130
-PLVD 30</t>
+    <t>HRSPV_98130</t>
   </si>
   <si>
     <t>14:35</t>
   </si>
   <si>
-    <t>WRSCH_98132
-PL 102</t>
-  </si>
-  <si>
-    <t>WRSCH_98134
-PL 104</t>
+    <t>HRSPV_98132</t>
+  </si>
+  <si>
+    <t>HRSPV_98134</t>
   </si>
   <si>
     <t>14:45</t>
   </si>
   <si>
-    <t>WRSCH_98544
-V 38
-X</t>
+    <t>HRSPV_98544</t>
   </si>
   <si>
     <t>15:19</t>
   </si>
   <si>
-    <t>WRSCH_98852
-B 52</t>
+    <t>HRSPV_98852</t>
   </si>
   <si>
     <t>15:41</t>
   </si>
   <si>
-    <t>WRSCH_98136
-PL 106
-X</t>
+    <t>HRSPV_98136</t>
   </si>
   <si>
     <t>14:56</t>
   </si>
   <si>
-    <t>WRSCH_98138
-PLVD 32</t>
+    <t>HRSPV_98138</t>
   </si>
   <si>
     <t>15:00</t>
   </si>
   <si>
-    <t>WRSCH_99042
-TPL 42</t>
+    <t>HRSPV_99042</t>
   </si>
   <si>
     <t>15:04</t>
   </si>
   <si>
-    <t>WRSCH_98546
-V 40
-X</t>
+    <t>HRSPV_98546</t>
   </si>
   <si>
     <t>15:33</t>
   </si>
   <si>
-    <t>WRSCH_98140
-PL 108</t>
+    <t>HRSPV_98140</t>
   </si>
   <si>
     <t>15:08</t>
   </si>
   <si>
-    <t>WRSCH_98752
-GN 52</t>
+    <t>HRSPV_98752</t>
   </si>
   <si>
     <t>15:35</t>
   </si>
   <si>
-    <t>WRSCH_98142
-PL 110</t>
+    <t>HRSPV_98142</t>
   </si>
   <si>
     <t>15:16</t>
   </si>
   <si>
-    <t>WRSCH_98144
-PL 112</t>
+    <t>HRSPV_98144</t>
   </si>
   <si>
     <t>15:20</t>
   </si>
   <si>
-    <t>WRSCH_98548
-VVD 8
-X</t>
+    <t>HRSPV_98548</t>
   </si>
   <si>
     <t>15:54</t>
   </si>
   <si>
-    <t>WRSCH_98854
-B 54</t>
+    <t>HRSPV_98854</t>
   </si>
   <si>
     <t>16:12</t>
   </si>
   <si>
-    <t>WRSCH_98146
-PL 114</t>
+    <t>HRSPV_98146</t>
   </si>
   <si>
     <t>15:28</t>
   </si>
   <si>
-    <t>WRSCH_98358
-BR 54</t>
+    <t>HRSPV_98358</t>
   </si>
   <si>
     <t>15:47</t>
   </si>
   <si>
-    <t>WRSCH_99044
-TPL 44</t>
+    <t>HRSPV_99044</t>
   </si>
   <si>
     <t>15:36</t>
   </si>
   <si>
-    <t>WRSCH_98754
-GN 54</t>
+    <t>HRSPV_98754</t>
   </si>
   <si>
     <t>16:01</t>
   </si>
   <si>
-    <t>WRSCH_98550
-V 42</t>
+    <t>HRSPV_98550</t>
   </si>
   <si>
     <t>16:11</t>
   </si>
   <si>
-    <t>WRSCH_98148
-PL 116</t>
+    <t>HRSPV_98148</t>
   </si>
   <si>
     <t>15:45</t>
   </si>
   <si>
-    <t>WRSCH_98150
-PL 118</t>
+    <t>HRSPV_98150</t>
   </si>
   <si>
     <t>15:49</t>
   </si>
   <si>
-    <t>WRSCH_98552
-VVD 10
-X</t>
+    <t>HRSPV_98552</t>
   </si>
   <si>
     <t>16:23</t>
   </si>
   <si>
-    <t>WRSCH_98856
-B 56
-X</t>
+    <t>HRSPV_98856</t>
   </si>
   <si>
     <t>16:41</t>
   </si>
   <si>
-    <t>WRSCH_99046
-TPL 46</t>
+    <t>HRSPV_99046</t>
   </si>
   <si>
     <t>15:53</t>
   </si>
   <si>
-    <t>WRSCH_98360
-BR 56
-X</t>
-  </si>
-  <si>
-    <t>WRSCH_98152
-PL 120
-X</t>
-  </si>
-  <si>
-    <t>WRSCH_98554
-VVD 12</t>
+    <t>HRSPV_98360</t>
+  </si>
+  <si>
+    <t>HRSPV_98152</t>
+  </si>
+  <si>
+    <t>HRSPV_98554</t>
   </si>
   <si>
     <t>16:35</t>
   </si>
   <si>
-    <t>WRSCH_98756
-GN 56</t>
+    <t>HRSPV_98756</t>
   </si>
   <si>
     <t>16:29</t>
   </si>
   <si>
-    <t>WRSCH_98154
-PL 122</t>
+    <t>HRSPV_98154</t>
   </si>
   <si>
     <t>16:10</t>
   </si>
   <si>
-    <t>WRSCH_99048
-TPL 48
-X</t>
+    <t>HRSPV_99048</t>
   </si>
   <si>
     <t>16:14</t>
   </si>
   <si>
-    <t>WRSCH_98556
-V 44</t>
+    <t>HRSPV_98556</t>
   </si>
   <si>
     <t>16:44</t>
   </si>
   <si>
-    <t>WRSCH_98362
-BR 58</t>
+    <t>HRSPV_98362</t>
   </si>
   <si>
     <t>16:33</t>
   </si>
   <si>
-    <t>WRSCH_98156
-PL 124
-X</t>
+    <t>HRSPV_98156</t>
   </si>
   <si>
     <t>16:22</t>
   </si>
   <si>
-    <t>WRSCH_98858
-B 58</t>
+    <t>HRSPV_98858</t>
   </si>
   <si>
     <t>17:13</t>
   </si>
   <si>
-    <t>WRSCH_98558
-VVD 14</t>
+    <t>HRSPV_98558</t>
   </si>
   <si>
     <t>16:55</t>
   </si>
   <si>
-    <t>WRSCH_99050
-TPL 50</t>
+    <t>HRSPV_99050</t>
   </si>
   <si>
     <t>16:26</t>
   </si>
   <si>
-    <t>WRSCH_98158
-PL 126</t>
+    <t>HRSPV_98158</t>
   </si>
   <si>
     <t>16:30</t>
   </si>
   <si>
-    <t>WRSCH_98758
-GN 58</t>
+    <t>HRSPV_98758</t>
   </si>
   <si>
     <t>16:58</t>
   </si>
   <si>
-    <t>WRSCH_98909
-PLGN 9</t>
+    <t>HRSPV_98909</t>
   </si>
   <si>
     <t>16:34</t>
   </si>
   <si>
-    <t>WRSCH_98160
-PL 128</t>
+    <t>HRSPV_98160</t>
   </si>
   <si>
     <t>16:38</t>
   </si>
   <si>
-    <t>WRSCH_98560
-V 46
-X</t>
+    <t>HRSPV_98560</t>
   </si>
   <si>
     <t>17:12</t>
   </si>
   <si>
-    <t>WRSCH_98860
-B 60</t>
+    <t>HRSPV_98860</t>
   </si>
   <si>
     <t>17:33</t>
   </si>
   <si>
-    <t>WRSCH_98162
-PLVD 34</t>
+    <t>HRSPV_98162</t>
   </si>
   <si>
     <t>16:45</t>
   </si>
   <si>
-    <t>WRSCH_98364
-BR 60</t>
+    <t>HRSPV_98364</t>
   </si>
   <si>
     <t>17:04</t>
   </si>
   <si>
-    <t>WRSCH_98164
-PL 130</t>
+    <t>HRSPV_98164</t>
   </si>
   <si>
     <t>16:53</t>
   </si>
   <si>
-    <t>WRSCH_98562
-V 48</t>
+    <t>HRSPV_98562</t>
   </si>
   <si>
     <t>17:27</t>
   </si>
   <si>
-    <t>WRSCH_98911
-PLGN 11</t>
+    <t>HRSPV_98911</t>
   </si>
   <si>
     <t>17:01</t>
   </si>
   <si>
-    <t>WRSCH_98760
-GN 60</t>
+    <t>HRSPV_98760</t>
   </si>
   <si>
     <t>17:25</t>
   </si>
   <si>
-    <t>WRSCH_98166
-PL 132</t>
+    <t>HRSPV_98166</t>
   </si>
   <si>
     <t>17:07</t>
   </si>
   <si>
-    <t>WRSCH_99052
-TPL 52</t>
-  </si>
-  <si>
-    <t>WRSCH_98564
-V 50</t>
+    <t>HRSPV_99052</t>
+  </si>
+  <si>
+    <t>HRSPV_98564</t>
   </si>
   <si>
     <t>17:44</t>
   </si>
   <si>
-    <t>WRSCH_98168
-PLVD 36</t>
+    <t>HRSPV_98168</t>
   </si>
   <si>
     <t>17:17</t>
   </si>
   <si>
-    <t>WRSCH_98862
-B 62</t>
+    <t>HRSPV_98862</t>
   </si>
   <si>
     <t>18:06</t>
   </si>
   <si>
-    <t>WRSCH_98170
-PL 134</t>
+    <t>HRSPV_98170</t>
   </si>
   <si>
     <t>17:21</t>
   </si>
   <si>
-    <t>WRSCH_98366
-BR 62
-X</t>
+    <t>HRSPV_98366</t>
   </si>
   <si>
     <t>17:40</t>
   </si>
   <si>
-    <t>WRSCH_98762
-GN 62</t>
+    <t>HRSPV_98762</t>
   </si>
   <si>
     <t>17:53</t>
   </si>
   <si>
-    <t>WRSCH_98913
-PLGN 13</t>
+    <t>HRSPV_98913</t>
   </si>
   <si>
     <t>17:29</t>
   </si>
   <si>
-    <t>WRSCH_98172
-PL 136</t>
-  </si>
-  <si>
-    <t>WRSCH_99054
-TPL 54
-$</t>
+    <t>HRSPV_98172</t>
+  </si>
+  <si>
+    <t>HRSPV_99054</t>
   </si>
   <si>
     <t>17:37</t>
   </si>
   <si>
-    <t>WRSCH_98566
-V 52
-X</t>
+    <t>HRSPV_98566</t>
   </si>
   <si>
     <t>18:07</t>
   </si>
   <si>
-    <t>WRSCH_98368
-BR 64</t>
+    <t>HRSPV_98368</t>
   </si>
   <si>
     <t>17:56</t>
   </si>
   <si>
-    <t>WRSCH_98864
-B 64</t>
+    <t>HRSPV_98864</t>
   </si>
   <si>
     <t>18:34</t>
   </si>
   <si>
-    <t>WRSCH_98174
-PLVD 38
-X</t>
+    <t>HRSPV_98174</t>
   </si>
   <si>
     <t>17:46</t>
   </si>
   <si>
-    <t>WRSCH_98176
-PL 138</t>
+    <t>HRSPV_98176</t>
   </si>
   <si>
     <t>17:50</t>
   </si>
   <si>
-    <t>WRSCH_98764
-GN 64</t>
+    <t>HRSPV_98764</t>
   </si>
   <si>
     <t>18:14</t>
   </si>
   <si>
-    <t>WRSCH_98568
-V 54
-X</t>
+    <t>HRSPV_98568</t>
   </si>
   <si>
     <t>18:26</t>
   </si>
   <si>
-    <t>WRSCH_99056
-TPL 56</t>
+    <t>HRSPV_99056</t>
   </si>
   <si>
     <t>17:57</t>
   </si>
   <si>
-    <t>WRSCH_98370
-BR 66</t>
+    <t>HRSPV_98370</t>
   </si>
   <si>
     <t>18:16</t>
   </si>
   <si>
-    <t>WRSCH_98910
-GNPL 10</t>
+    <t>HRSPV_98910</t>
   </si>
   <si>
     <t>18:27</t>
   </si>
   <si>
-    <t>WRSCH_98178
-PL 140</t>
-  </si>
-  <si>
-    <t>WRSCH_98866
-B 66</t>
+    <t>HRSPV_98178</t>
+  </si>
+  <si>
+    <t>HRSPV_98866</t>
   </si>
   <si>
     <t>19:01</t>
   </si>
   <si>
-    <t>WRSCH_98180
-PL 142
-X</t>
-  </si>
-  <si>
-    <t>WRSCH_98766
-GN 66
-X</t>
+    <t>HRSPV_98180</t>
+  </si>
+  <si>
+    <t>HRSPV_98766</t>
   </si>
   <si>
     <t>18:41</t>
   </si>
   <si>
-    <t>WRSCH_98182
-PLVD 40</t>
+    <t>HRSPV_98182</t>
   </si>
   <si>
     <t>18:18</t>
   </si>
   <si>
-    <t>WRSCH_99058
-TPL 58
-$</t>
+    <t>HRSPV_99058</t>
   </si>
   <si>
     <t>18:22</t>
   </si>
   <si>
-    <t>WRSCH_98570
-V 56</t>
+    <t>HRSPV_98570</t>
   </si>
   <si>
     <t>18:54</t>
   </si>
   <si>
-    <t>WRSCH_98372
-BR 68
-X</t>
+    <t>HRSPV_98372</t>
   </si>
   <si>
     <t>18:44</t>
   </si>
   <si>
-    <t>WRSCH_98868
-B 68</t>
+    <t>HRSPV_98868</t>
   </si>
   <si>
     <t>19:22</t>
   </si>
   <si>
-    <t>WRSCH_98915
-PLGN 15</t>
+    <t>HRSPV_98915</t>
   </si>
   <si>
     <t>18:33</t>
   </si>
   <si>
-    <t>WRSCH_98184
-PL 144</t>
+    <t>HRSPV_98184</t>
   </si>
   <si>
     <t>18:37</t>
   </si>
   <si>
-    <t>WRSCH_98912
-GNPL 12</t>
+    <t>HRSPV_98912</t>
   </si>
   <si>
     <t>18:55</t>
   </si>
   <si>
-    <t>WRSCH_98186
-PL 146</t>
-  </si>
-  <si>
-    <t>WRSCH_98572
-V 58</t>
+    <t>HRSPV_98186</t>
+  </si>
+  <si>
+    <t>HRSPV_98572</t>
   </si>
   <si>
     <t>19:15</t>
   </si>
   <si>
-    <t>WRSCH_98188
-PLVD 42</t>
+    <t>HRSPV_98188</t>
   </si>
   <si>
     <t>18:49</t>
   </si>
   <si>
-    <t>WRSCH_98768
-GN 68</t>
+    <t>HRSPV_98768</t>
   </si>
   <si>
     <t>19:10</t>
   </si>
   <si>
-    <t>WRSCH_98190
-PL 148</t>
+    <t>HRSPV_98190</t>
   </si>
   <si>
     <t>18:57</t>
   </si>
   <si>
-    <t>WRSCH_98770
-GN 70</t>
+    <t>HRSPV_98770</t>
   </si>
   <si>
     <t>19:27</t>
   </si>
   <si>
-    <t>WRSCH_99060
-TPL 60</t>
-  </si>
-  <si>
-    <t>WRSCH_98374
-BRVD 6
-X</t>
+    <t>HRSPV_99060</t>
+  </si>
+  <si>
+    <t>HRSPV_98374</t>
   </si>
   <si>
     <t>19:20</t>
   </si>
   <si>
-    <t>WRSCH_98192
-PL 150</t>
+    <t>HRSPV_98192</t>
   </si>
   <si>
     <t>19:09</t>
   </si>
   <si>
-    <t>WRSCH_99062
-TPL 62</t>
+    <t>HRSPV_99062</t>
   </si>
   <si>
     <t>19:13</t>
   </si>
   <si>
-    <t>WRSCH_98870
-B 70</t>
+    <t>HRSPV_98870</t>
   </si>
   <si>
     <t>20:02</t>
   </si>
   <si>
-    <t>WRSCH_98194
-PL 152</t>
+    <t>HRSPV_98194</t>
   </si>
   <si>
     <t>19:17</t>
   </si>
   <si>
-    <t>WRSCH_98914
-GNPL 14</t>
+    <t>HRSPV_98914</t>
   </si>
   <si>
     <t>19:40</t>
   </si>
   <si>
-    <t>WRSCH_91396
-WGN 6</t>
+    <t>HRSPV_91396</t>
   </si>
   <si>
     <t>19:45</t>
   </si>
   <si>
-    <t>WRSCH_98196
-PL 154</t>
+    <t>HRSPV_98196</t>
   </si>
   <si>
     <t>19:24</t>
   </si>
   <si>
-    <t>WRSCH_98772
-GN 72</t>
+    <t>HRSPV_98772</t>
   </si>
   <si>
     <t>19:56</t>
   </si>
   <si>
-    <t>WRSCH_99064
-TPL 64</t>
+    <t>HRSPV_99064</t>
   </si>
   <si>
     <t>19:31</t>
   </si>
   <si>
-    <t>WRSCH_98917
-PLGN 17</t>
+    <t>HRSPV_98917</t>
   </si>
   <si>
     <t>19:35</t>
   </si>
   <si>
-    <t>WRSCH_98574
-V 60
-X</t>
+    <t>HRSPV_98574</t>
   </si>
   <si>
     <t>20:09</t>
   </si>
   <si>
-    <t>WRSCH_98198
-PL 156</t>
+    <t>HRSPV_98198</t>
   </si>
   <si>
     <t>19:43</t>
   </si>
   <si>
-    <t>WRSCH_98872
-B 72</t>
+    <t>HRSPV_98872</t>
   </si>
   <si>
     <t>20:33</t>
   </si>
   <si>
-    <t>WRSCH_98376
-BRVD 8
-X</t>
-  </si>
-  <si>
-    <t>WRSCH_98200
-PL 158</t>
+    <t>HRSPV_98376</t>
+  </si>
+  <si>
+    <t>HRSPV_98200</t>
   </si>
   <si>
     <t>19:51</t>
   </si>
   <si>
-    <t>WRSCH_98916
-GNPL 16</t>
+    <t>HRSPV_98916</t>
   </si>
   <si>
     <t>20:12</t>
   </si>
   <si>
-    <t>WRSCH_98202
-PL 160</t>
+    <t>HRSPV_98202</t>
   </si>
   <si>
     <t>19:55</t>
   </si>
   <si>
-    <t>WRSCH_98576
-V 62
-X</t>
+    <t>HRSPV_98576</t>
   </si>
   <si>
     <t>20:29</t>
   </si>
   <si>
-    <t>WRSCH_98378
-BRVD 10</t>
+    <t>HRSPV_98378</t>
   </si>
   <si>
     <t>20:18</t>
   </si>
   <si>
-    <t>WRSCH_98774
-GN 74</t>
+    <t>HRSPV_98774</t>
   </si>
   <si>
     <t>20:26</t>
   </si>
   <si>
-    <t>WRSCH_98204
-PL 162</t>
+    <t>HRSPV_98204</t>
   </si>
   <si>
     <t>20:07</t>
   </si>
   <si>
-    <t>WRSCH_98874
-B 74</t>
+    <t>HRSPV_98874</t>
   </si>
   <si>
     <t>20:59</t>
   </si>
   <si>
-    <t>WRSCH_98380
-BR 70
-X</t>
+    <t>HRSPV_98380</t>
   </si>
   <si>
     <t>20:30</t>
   </si>
   <si>
-    <t>WRSCH_98578
-V 64
-X</t>
+    <t>HRSPV_98578</t>
   </si>
   <si>
     <t>20:49</t>
   </si>
   <si>
-    <t>WRSCH_99066
-TPL 66</t>
+    <t>HRSPV_99066</t>
   </si>
   <si>
     <t>20:19</t>
   </si>
   <si>
-    <t>WRSCH_98206
-PL 164</t>
+    <t>HRSPV_98206</t>
   </si>
   <si>
     <t>20:23</t>
   </si>
   <si>
-    <t>WRSCH_98776
-GN 76</t>
+    <t>HRSPV_98776</t>
   </si>
   <si>
     <t>20:51</t>
   </si>
   <si>
-    <t>WRSCH_98208
-PLVD 44
-X</t>
+    <t>HRSPV_98208</t>
   </si>
   <si>
     <t>20:27</t>
   </si>
   <si>
-    <t>WRSCH_98210
-PL 166</t>
+    <t>HRSPV_98210</t>
   </si>
   <si>
     <t>20:31</t>
   </si>
   <si>
-    <t>WRSCH_98212
-PL 168</t>
+    <t>HRSPV_98212</t>
   </si>
   <si>
     <t>20:35</t>
   </si>
   <si>
-    <t>WRSCH_98382
-BR 72</t>
+    <t>HRSPV_98382</t>
   </si>
   <si>
     <t>20:54</t>
   </si>
   <si>
-    <t>WRSCH_98876
-B 76</t>
+    <t>HRSPV_98876</t>
   </si>
   <si>
     <t>21:31</t>
   </si>
   <si>
-    <t>WRSCH_98214
-PL 170</t>
+    <t>HRSPV_98214</t>
   </si>
   <si>
     <t>20:47</t>
   </si>
   <si>
-    <t>WRSCH_99068
-TPL 68
-X</t>
-  </si>
-  <si>
-    <t>WRSCH_98778
-GN 78</t>
+    <t>HRSPV_99068</t>
+  </si>
+  <si>
+    <t>HRSPV_98778</t>
   </si>
   <si>
     <t>21:15</t>
   </si>
   <si>
-    <t>WRSCH_98216
-PL 172</t>
+    <t>HRSPV_98216</t>
   </si>
   <si>
     <t>20:57</t>
   </si>
   <si>
-    <t>WRSCH_98384
-BR 74
-X</t>
+    <t>HRSPV_98384</t>
   </si>
   <si>
     <t>21:16</t>
   </si>
   <si>
-    <t>WRSCH_98918
-GNPL 18</t>
+    <t>HRSPV_98918</t>
   </si>
   <si>
     <t>21:28</t>
   </si>
   <si>
-    <t>WRSCH_98218
-PL 174</t>
+    <t>HRSPV_98218</t>
   </si>
   <si>
     <t>21:05</t>
   </si>
   <si>
-    <t>WRSCH_98878
-B 78</t>
+    <t>HRSPV_98878</t>
   </si>
   <si>
     <t>22:00</t>
   </si>
   <si>
-    <t>WRSCH_98220
-PL 176</t>
-  </si>
-  <si>
-    <t>WRSCH_98780
-GN 80</t>
+    <t>HRSPV_98220</t>
+  </si>
+  <si>
+    <t>HRSPV_98780</t>
   </si>
   <si>
     <t>21:43</t>
   </si>
   <si>
-    <t>WRSCH_99070
-TPL 70</t>
+    <t>HRSPV_99070</t>
   </si>
   <si>
     <t>21:20</t>
   </si>
   <si>
-    <t>WRSCH_98222
-PL 178</t>
+    <t>HRSPV_98222</t>
   </si>
   <si>
     <t>21:26</t>
   </si>
   <si>
-    <t>WRSCH_98224
-PL 180
-X</t>
+    <t>HRSPV_98224</t>
   </si>
   <si>
     <t>21:30</t>
   </si>
   <si>
-    <t>WRSCH_98880
-B 80</t>
+    <t>HRSPV_98880</t>
   </si>
   <si>
     <t>22:24</t>
   </si>
   <si>
-    <t>WRSCH_98226
-PL 182</t>
+    <t>HRSPV_98226</t>
   </si>
   <si>
     <t>21:39</t>
   </si>
   <si>
-    <t>WRSCH_98782
-GN 82</t>
+    <t>HRSPV_98782</t>
   </si>
   <si>
     <t>22:15</t>
   </si>
   <si>
-    <t>WRSCH_98228
-PL 184</t>
+    <t>HRSPV_98228</t>
   </si>
   <si>
     <t>21:52</t>
   </si>
   <si>
-    <t>WRSCH_98882
-B 82</t>
+    <t>HRSPV_98882</t>
   </si>
   <si>
     <t>22:49</t>
   </si>
   <si>
-    <t>WRSCH_98230
-PL 186
-X</t>
+    <t>HRSPV_98230</t>
   </si>
   <si>
     <t>22:07</t>
   </si>
   <si>
-    <t>WRSCH_99072
-TPL 72</t>
-  </si>
-  <si>
-    <t>WRSCH_98784
-GN 84</t>
+    <t>HRSPV_99072</t>
+  </si>
+  <si>
+    <t>HRSPV_98784</t>
   </si>
   <si>
     <t>22:40</t>
   </si>
   <si>
-    <t>WRSCH_98232
-PL 188</t>
+    <t>HRSPV_98232</t>
   </si>
   <si>
     <t>22:19</t>
   </si>
   <si>
-    <t>WRSCH_98234
-PL 190</t>
+    <t>HRSPV_98234</t>
   </si>
   <si>
     <t>22:23</t>
   </si>
   <si>
-    <t>WRSCH_98884
-B 84</t>
+    <t>HRSPV_98884</t>
   </si>
   <si>
     <t>23:16</t>
   </si>
   <si>
-    <t>WRSCH_98236
-PL 192</t>
+    <t>HRSPV_98236</t>
   </si>
   <si>
     <t>22:35</t>
   </si>
   <si>
-    <t>WRSCH_98786
-GN 86</t>
+    <t>HRSPV_98786</t>
   </si>
   <si>
     <t>23:06</t>
   </si>
   <si>
-    <t>WRSCH_98238
-PL 194</t>
+    <t>HRSPV_98238</t>
   </si>
   <si>
     <t>22:46</t>
   </si>
   <si>
-    <t>WRSCH_98240
-VPL 2
-X</t>
+    <t>HRSPV_98240</t>
   </si>
   <si>
     <t>HRTR0168OR</t>
@@ -2498,43 +2089,37 @@
     <t>22:50</t>
   </si>
   <si>
-    <t>WRSCH_98886
-B 86</t>
+    <t>HRSPV_98886</t>
   </si>
   <si>
     <t>23:42</t>
   </si>
   <si>
-    <t>WRSCH_98242
-PL 196</t>
+    <t>HRSPV_98242</t>
   </si>
   <si>
     <t>22:58</t>
   </si>
   <si>
-    <t>WRSCH_98788
-GN 88</t>
+    <t>HRSPV_98788</t>
   </si>
   <si>
     <t>23:33</t>
   </si>
   <si>
-    <t>WRSCH_98244
-PL 198</t>
+    <t>HRSPV_98244</t>
   </si>
   <si>
     <t>23:13</t>
   </si>
   <si>
-    <t>WRSCH_99074
-TPL 74</t>
+    <t>HRSPV_99074</t>
   </si>
   <si>
     <t>23:18</t>
   </si>
   <si>
-    <t>WRSCH_98246
-BRPL 2</t>
+    <t>HRSPV_98246</t>
   </si>
   <si>
     <t>HRTR0169OR</t>
@@ -2543,30 +2128,24 @@
     <t>23:22</t>
   </si>
   <si>
-    <t>WRSCH_98248
-VPL 4</t>
+    <t>HRSPV_98248</t>
   </si>
   <si>
     <t>23:32</t>
   </si>
   <si>
-    <t>WRSCH_98250
-PLVD 46</t>
+    <t>HRSPV_98250</t>
   </si>
   <si>
     <t>23:36</t>
   </si>
   <si>
-    <t>WRSCH_98252
-BRPL 4</t>
+    <t>HRSPV_98252</t>
   </si>
   <si>
     <t>23:48</t>
   </si>
   <si>
-    <t>WRSCH_AC</t>
-  </si>
-  <si>
     <t>HRTR0170AC</t>
   </si>
   <si>
@@ -2583,6 +2162,21 @@
   </si>
   <si>
     <t>HRTR0174AC</t>
+  </si>
+  <si>
+    <t>HRSPV_1AC</t>
+  </si>
+  <si>
+    <t>HRSPV_2AC</t>
+  </si>
+  <si>
+    <t>HRSPV_3AC</t>
+  </si>
+  <si>
+    <t>HRSPV_4AC</t>
+  </si>
+  <si>
+    <t>HRSPV_5AC</t>
   </si>
 </sst>
 </file>
@@ -2925,8 +2519,8 @@
   <dimension ref="A1:E370"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -8983,10 +8577,10 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
+        <v>714</v>
+      </c>
+      <c r="B357" t="s">
         <v>708</v>
-      </c>
-      <c r="B357" t="s">
-        <v>709</v>
       </c>
       <c r="C357" t="s">
         <v>23</v>
@@ -9000,10 +8594,10 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B358" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C358" t="s">
         <v>11</v>
@@ -9017,10 +8611,10 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="B359" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C359" t="s">
         <v>19</v>
@@ -9034,10 +8628,10 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B360" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C360" t="s">
         <v>11</v>
@@ -9051,10 +8645,10 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B361" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C361" t="s">
         <v>11</v>
@@ -9068,10 +8662,10 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B362" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C362" t="s">
         <v>11</v>
@@ -9085,10 +8679,10 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B363" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C363" t="s">
         <v>11</v>
@@ -9102,10 +8696,10 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="B364" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C364" t="s">
         <v>19</v>
@@ -9119,16 +8713,16 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="B365" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C365" t="s">
         <v>19</v>
       </c>
       <c r="D365" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E365">
         <v>7</v>
@@ -9136,10 +8730,10 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B366" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C366" t="s">
         <v>11</v>
@@ -9153,10 +8747,10 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B367" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C367" t="s">
         <v>11</v>
@@ -9170,10 +8764,10 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B368" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C368" t="s">
         <v>11</v>
@@ -9187,10 +8781,10 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B369" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C369" t="s">
         <v>11</v>
@@ -9204,10 +8798,10 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="B370" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C370" t="s">
         <v>11</v>
